--- a/data_extactor/batch_10_fa/trimmed/batch_0080_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0080_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نظارت | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | حمل‌ونقل | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>مکانیک | حمل و نقل | ایمنی و امنیت عمومی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | دقت کنترل | حساسیت شنوایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | مکانیک و تکنسین ماشین‌آلات کشاورزی | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار</t>
+          <t>مکانیک و تکنسین خدمات خودرو | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | تعمیرکار واگن قطار</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | نظارت | یادگیری فعال | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | نظارت | یادگیری فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | دقت کنترل | هماهنگی اندام‌ها | چابکی دستی | حساسیت به مسئله | دید نزدیک | ثبات دست و بازو</t>
+          <t>مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | حساسیت به مسئله | بینایی نزدیک | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>اپراتور ادوات و ماشین‌آلات کشاورزی | تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک ماشین‌آلات صنعتی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز</t>
+          <t>اپراتورهای ماشین‌آلات و ادوات کشاورزی | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک تجهیزات سنگین متحرک | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | یادگیری فعال | سخن گفتن | نگارش</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ریاضیات | رایانه و الکترونیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>چابکی دستی | دقت کنترل | چابکی انگشتان | دید نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی اندام‌ها</t>
+          <t>مهارت دستی | دقت کنترل | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله | ثبات دست و بازو | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتور جرثقیل و تاورکرین | مکانیک و تکنسین ماشین‌آلات کشاورزی | مکانیک ماشین‌آلات صنعتی | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | اپراتور ماشین‌آلات سنگین راه‌سازی و ساختمانی</t>
+          <t>مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | اپراتورهای جرثقیل و تاورکرین | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مکانیک‌های ماشین‌آلات صنعتی | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مکانیک | تولید و فرآوری | ساختمان و سازه | مهندسی و فناوری | حمل‌ونقل | ریاضیات</t>
+          <t>مکانیک | تولید و فرآوری | ساختمان و ساخت‌وساز | مهندسی و فناوری | حمل و نقل | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | چابکی دستی | دقت کنترل | هماهنگی اندام‌ها | چابکی انگشتان | دید نزدیک | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت دستی | دقت کنترل | هماهنگی چند عضو | مهارت انگشتان | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک ماشین‌آلات صنعتی | کارگر عمومی تعمیر و نگهداری | نصاب و مونتاژکار ماشین‌آلات صنعتی (میل‌رایت) | اپراتور ماشین‌آلات ریل‌گذاری و نگهداری خطوط راه‌آهن | تعمیرکار علائم، سوزن و تجهیزات کنترل خطوط ریلی</t>
+          <t>مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | اپراتورهای ماشین‌آلات روسازی و نگهداری خطوط راه‌آهن | تعمیرکاران علائم، سیگنال‌ها و سوزن‌های راه‌آهن</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | حمل‌ونقل</t>
+          <t>مکانیک | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | حمل و نقل</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | چابکی دستی | استدلال قیاسی | ثبات دست و بازو | چابکی انگشتان | دقت کنترل | دید نزدیک</t>
+          <t>حساسیت به مسئله | مهارت دستی | استدلال قیاسی | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مونتاژکار موتور و سایر ماشین‌آلات | مکانیک ماشین‌آلات صنعتی | مهندس شناورهای دریایی و معمار دریایی | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز</t>
+          <t>مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مونتاژکاران موتور و سایر ماشین‌آلات | مکانیک‌های ماشین‌آلات صنعتی | مهندسان دریایی و معماران کشتی | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش</t>
+          <t>مکانیک | زبان انگلیسی | خدمات مشتری و شخصی | رایانه و الکترونیک | ریاضیات | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | چابکی دستی | چابکی انگشتان | دید نزدیک | حساسیت شنوایی | ثبات دست و بازو | حساسیت به مسئله</t>
+          <t>استدلال قیاسی | مهارت دستی | مهارت انگشتان | بینایی نزدیک | حساسیت شنوایی | ثبات دست و بازو | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
+          <t>صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | تعمیرکار دوچرخه | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | حمل‌ونقل | فروش و بازاریابی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | آموزش و پرورش | حمل و نقل | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | ثبات دست و بازو | چابکی دستی | دید نزدیک | دقت کنترل | تجسم فضایی | حساسیت به مسئله</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | دقت کنترل | تجسم | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | تعمیرکار دوچرخه | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مکانیک و تکنسین ماشین‌آلات کشاورزی | تعمیرکار لوازم خانگی | کارگر تعمیر و نگهداری ماشین‌آلات | مکانیک موتورسیکلت</t>
+          <t>مکانیک و تکنسین خدمات خودرو | تعمیرکار دوچرخه | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | تعمیرکاران لوازم خانگی | کارگران تعمیر و نگهداری ماشین‌آلات | مکانیک موتورسیکلت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>فیتِر دوچرخه (تنظیم‌کننده تخصصی دوچرخه) | مکانیک دوچرخه | تکنسین تعمیرات دوچرخه | تعمیرکار دوچرخه | تکنسین خدمات دوچرخه | تکنسین دوچرخه | مکانیک دوچرخه</t>
+          <t>فیتِر دوچرخه (تنظیم‌کننده تخصصی دوچرخه) | مکانیک دوچرخه | تکنسین تعمیرات دوچرخه | تعمیرکار دوچرخه | تکنسین خدمات دوچرخه | تکنسین دوچرخه</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | فروش و بازاریابی | مهندسی و فناوری | مدیریت و امور اداری | تولید و فرآوری</t>
+          <t>مکانیک | خدمات مشتری و شخصی | فروش و بازاریابی | مهندسی و فناوری | مدیریت و اداره | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | چابکی انگشتان | دید نزدیک | ثبات دست و بازو | چابکی دستی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>تجسم | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین خدمات و مکانیک خودرو | تعمیرکار موتور برقی، ابزار برقی و تجهیزات وابسته | مونتاژکار موتور و سایر ماشین‌آلات | کمک‌کارگر نصب، تعمیر و نگهداری | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
+          <t>مکانیک و تکنسین خدمات خودرو | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران کمکی نصب، نگهداری و تعمیرات | مکانیک موتورسیکلت | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>یادگیری فعال | تفکر انتقادی | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مدیریت و اداره | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی دستی | حساسیت به مسئله | چابکی انگشتان | دقت کنترل | درک شفاهی | ثبات دست و بازو</t>
+          <t>بینایی نزدیک | مهارت دستی | حساسیت به مسئله | مهارت انگشتان | دقت کنترل | درک شفاهی | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو و تعمیرکار بدنه | تکنسین خدمات و مکانیک خودرو | نصاب و تعمیرکار تجهیزات الکترونیکی خودرو | مکانیک و نصاب تاسیسات سرمایشی، گرمایشی و تهویه مطبوع | تعمیرکار لوازم خانگی | کارگر عمومی تعمیر و نگهداری | لوله‌کش، تاسیسات‌کار و مونتاژکار لوله‌های بخار</t>
+          <t>صافکار و نقاش خودرو | مکانیک و تکنسین خدمات خودرو | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,22 +1016,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>نرم‌افزار برآورد و تخمین هزینه‌ها | نرم‌افزار ثبت سوابق فنی | Microsoft Excel | Microsoft Outlook | Microsoft Word</t>
+          <t>نرم‌افزار برآورد و تخمین هزینه‌ها | نرم‌افزار ثبت سوابق فنی | Microsoft Excel | Microsoft Outlook | نرم‌افزار ثبت سوابق</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | فروش و بازاریابی</t>
+          <t>مکانیک | خدمات مشتری و شخصی | مدیریت و اداره | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>قدرت بالاتنه | چابکی دستی | هماهنگی اندام‌ها | قدرت ایستا | دید نزدیک | دقت کنترل | ثبات دست و بازو</t>
+          <t>قدرت تنه | مهارت دستی | هماهنگی چند عضو | قدرت ایستا | بینایی نزدیک | دقت کنترل | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>صافکار و نقاش خودرو و تعمیرکار بدنه | نصاب و تعمیرکار شیشه خودرو | تکنسین خدمات و مکانیک خودرو | متصدی خدمات خودرو و شناورها | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک موتورسیکلت | سازنده تایر</t>
+          <t>صافکار و نقاش خودرو | نصاب و تعمیرکار شیشه خودرو | مکانیک و تکنسین خدمات خودرو | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | مکانیک موتورسیکلت | سازندگان تایر</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
